--- a/GATEWAY/A1#111#MILLENIUMSPAXX/MILLENNIUMSPA/MILLEWEB/1.101.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#MILLENIUMSPAXX/MILLENNIUMSPA/MILLEWEB/1.101.0/report-checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gmhservice-my.sharepoint.com/personal/antonietta_devito_millennium_it/Documents/Desktop/temp/MILLEWEB-ACCREDITAMENTO 1.5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\francesco.micchetti.MILLENNIUM\Documents\work\data\FSE2.0\Accreditamento\2026.04.10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{D28448E2-CC9C-4A71-8064-75D3FFC26D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D965EC44-CAED-4355-8BBB-59CB6F26B94D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B212B6AD-299B-4D1F-BBBC-844497774026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -1888,13 +1888,13 @@
     <t>subject_application_vendor: MILLENNIUM SPA</t>
   </si>
   <si>
-    <t>2026-04-09T09:25:24Z</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.20.4.4.1c2146b6520077a6d38ebed3b2ce8e55742a039ae1cc631eb79e72ea3a83cc72.368237c348^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>5b51fd4c63e8cd7a42d442e8e99434ab</t>
+    <t>2026-04-10T11:09:24Z</t>
+  </si>
+  <si>
+    <t>9aac10ac1f31e4d2a57ef57563cce469</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.20.4.4.398ddb678adb708246539cc3f538fdf1322e57de4e249f5f7a6de8614951f813.a690006fe1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>subject_application_id: MILLEWEB</t>
@@ -11210,16 +11210,16 @@
         <v>437</v>
       </c>
       <c r="F193" s="37">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="G193" s="37" t="s">
         <v>461</v>
       </c>
       <c r="H193" s="37" t="s">
+        <v>462</v>
+      </c>
+      <c r="I193" s="42" t="s">
         <v>463</v>
-      </c>
-      <c r="I193" s="42" t="s">
-        <v>462</v>
       </c>
       <c r="J193" s="38" t="s">
         <v>64</v>
